--- a/excel/CutsceneData.xlsx
+++ b/excel/CutsceneData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6B5A6D7-83B7-EC4B-AA5A-EE5841BE5F63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9473B66-322E-814E-BE0D-085E2E2BB89C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4160" yWindow="680" windowWidth="24700" windowHeight="14700" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4160" yWindow="680" windowWidth="24700" windowHeight="14700" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CutsceneInfo" sheetId="1" r:id="rId1"/>
@@ -22,11 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="93">
-  <si>
-    <t>AlwaysTrue</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="96">
   <si>
     <t>list&lt;int&gt;</t>
   </si>
@@ -417,10 +413,6 @@
   </si>
   <si>
     <t>...</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>AlwaysFalse</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -1122,6 +1114,135 @@
   </si>
   <si>
     <t>날아갔다…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>None</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>파우더상점</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>구매</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>파우더상점</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>구매</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>리피파이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>여긴 지솜님이 다음 빌드에 작업할거야.</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1622,63 +1743,63 @@
   <sheetData>
     <row r="1" spans="1:8" s="10" customFormat="1" ht="15.75" customHeight="1">
       <c r="A1" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C1" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="9" t="s">
-        <v>6</v>
-      </c>
       <c r="E1" s="9" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="12" customFormat="1" ht="15.75" customHeight="1">
       <c r="A2" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C2" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="11" t="s">
-        <v>10</v>
-      </c>
       <c r="E2" s="11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="11" t="s">
-        <v>3</v>
-      </c>
       <c r="H2" s="11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15">
       <c r="A3" s="14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="2" t="s">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="4">
@@ -1690,11 +1811,11 @@
     </row>
     <row r="4" spans="1:8" ht="13">
       <c r="A4" s="14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B4" s="21"/>
       <c r="C4" s="2" t="s">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="E4" s="4">
         <v>1</v>
@@ -1703,10 +1824,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="13">
-      <c r="A5" s="3"/>
+    <row r="5" spans="1:8" ht="15">
+      <c r="A5" s="3" t="s">
+        <v>92</v>
+      </c>
       <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
+      <c r="C5" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E5" s="4">
+        <v>1</v>
+      </c>
+      <c r="H5" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:8" ht="13">
       <c r="A6" s="7"/>
@@ -1738,66 +1869,66 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B1" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="22" t="s">
-        <v>6</v>
-      </c>
       <c r="D1" s="15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E1" s="22" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="C2" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="23" t="s">
-        <v>33</v>
-      </c>
       <c r="D2" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" s="23" t="s">
         <v>37</v>
-      </c>
-      <c r="E2" s="23" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15">
       <c r="A3" s="14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C3" s="24"/>
       <c r="D3" s="17" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15">
       <c r="A4" s="14" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C4" s="24"/>
       <c r="D4" s="17" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1809,7 +1940,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="20.33203125" customWidth="1"/>
@@ -1822,793 +1953,813 @@
   <sheetData>
     <row r="1" spans="1:7" s="16" customFormat="1">
       <c r="A1" s="15" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G1" s="18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="16" customFormat="1">
       <c r="A2" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="15" t="s">
-        <v>13</v>
-      </c>
       <c r="C2" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E2" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="15" t="s">
-        <v>18</v>
-      </c>
       <c r="G2" s="18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D3" s="26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G3" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15">
       <c r="A4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B4">
         <v>2</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E4" s="27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F4" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="19" t="s">
         <v>26</v>
-      </c>
-      <c r="G4" s="19" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15">
       <c r="A5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B5">
         <v>3</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15">
       <c r="A6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15">
       <c r="A7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B7">
         <v>2</v>
       </c>
       <c r="C7" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="17" t="s">
-        <v>54</v>
-      </c>
       <c r="E7" s="27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G7" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15">
       <c r="A8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B8">
         <v>3</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E8" s="27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G8" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15">
       <c r="A9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B9">
         <v>4</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G9" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15">
       <c r="A10" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B10">
         <v>5</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="32">
       <c r="A11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B11">
         <v>6</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G11" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15">
       <c r="A12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B12">
         <v>7</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E12" s="27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G12" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B13">
         <v>8</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G13" s="19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15">
       <c r="A14" s="14" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B14">
         <v>9</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G14" s="19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="48">
       <c r="A15" s="14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B15">
         <v>10</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D15" s="28" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G15" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15">
       <c r="A16" s="14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B16">
         <v>11</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G16" s="19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15">
       <c r="A17" s="14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B17">
         <v>12</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F17" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G17" s="19" t="s">
         <v>26</v>
-      </c>
-      <c r="G17" s="19" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="16">
       <c r="A18" s="14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B18">
         <v>13</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D18" s="28" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E18" s="27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G18" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="48">
       <c r="A19" s="14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B19">
         <v>14</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D19" s="28" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G19" s="19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="16">
       <c r="A20" s="14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B20">
         <v>15</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D20" s="28" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E20" s="27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G20" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="16">
       <c r="A21" s="14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B21">
         <v>16</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D21" s="28" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G21" s="19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B22">
         <v>17</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B23">
         <v>18</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F23" s="14"/>
     </row>
     <row r="24" spans="1:7" ht="16">
       <c r="A24" s="14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B24">
         <v>19</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D24" s="28" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G24" s="19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="32">
       <c r="A25" s="14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B25">
         <v>20</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D25" s="28" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E25" s="27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G25" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="64">
       <c r="A26" s="14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B26">
         <v>21</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D26" s="28" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F26" s="14"/>
       <c r="G26" s="19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="48">
       <c r="A27" s="14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B27">
         <v>22</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D27" s="28" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F27" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G27" s="19" t="s">
         <v>26</v>
-      </c>
-      <c r="G27" s="19" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="80">
       <c r="A28" s="14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B28">
         <v>23</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D28" s="28" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E28" s="27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G28" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="128">
       <c r="A29" s="14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B29">
         <v>24</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D29" s="28" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E29" s="27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G29" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="80">
       <c r="A30" s="14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B30">
         <v>25</v>
       </c>
       <c r="C30" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="D30" s="28" t="s">
         <v>82</v>
       </c>
-      <c r="D30" s="28" t="s">
-        <v>84</v>
-      </c>
       <c r="E30" s="27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G30" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="80">
       <c r="A31" s="14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B31">
         <v>26</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D31" s="28" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E31" s="27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G31" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="64">
       <c r="A32" s="14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B32">
         <v>27</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D32" s="28" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F32" s="14"/>
       <c r="G32" s="19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="48">
       <c r="A33" s="14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B33">
         <v>28</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D33" s="28" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E33" s="27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G33" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34" spans="1:7" s="32" customFormat="1" ht="80">
       <c r="A34" s="14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B34" s="32">
         <v>29</v>
       </c>
       <c r="C34" s="29" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D34" s="30" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E34" s="31" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G34" s="33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="48">
       <c r="A35" s="14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B35">
         <v>30</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D35" s="28" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E35" s="27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G35" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="16">
       <c r="A36" s="14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B36">
         <v>31</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D36" s="28" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F36" s="14"/>
       <c r="G36" s="19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="64">
       <c r="A37" s="14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B37">
         <v>32</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D37" s="28" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E37" s="27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G37" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B38">
         <v>33</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F38" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B39">
         <v>34</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F39" s="14"/>
     </row>
     <row r="40" spans="1:7" ht="16">
       <c r="A40" s="14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B40">
         <v>35</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D40" s="28" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F40" s="14"/>
       <c r="G40" s="19" t="s">
-        <v>27</v>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="32">
+      <c r="A41" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="B41">
+        <v>1</v>
+      </c>
+      <c r="C41" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D41" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="E41" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="G41" s="19" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/excel/CutsceneData.xlsx
+++ b/excel/CutsceneData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9473B66-322E-814E-BE0D-085E2E2BB89C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F71FBA6C-B683-BA42-A831-FE03EFFA282C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4160" yWindow="680" windowWidth="24700" windowHeight="14700" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="96">
   <si>
     <t>list&lt;int&gt;</t>
   </si>
@@ -217,27 +217,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Malgun Gothic"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>마이홈</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="3"/>
+        <family val="2"/>
         <charset val="129"/>
       </rPr>
       <t>슬라임</t>
@@ -248,172 +228,9 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>말걸기</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
       </rPr>
       <t>]</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>마이홈</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>슬라임</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>말걸기</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>이건</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>뭐지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>?</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>슬라임</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
-    <t>보글보글</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>...</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1117,10 +934,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>None</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>[</t>
     </r>
@@ -1244,13 +1057,300 @@
   <si>
     <t>여긴 지솜님이 다음 빌드에 작업할거야.</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>슬라임미니게임</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Roboto"/>
+        <family val="1"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아티팩트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Roboto"/>
+        <family val="1"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>필요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Roboto"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>슬라임미니게임</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>아티팩트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>필요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>슬라임</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>아티팩트가 없다!</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>파우더미니게임</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아티팩트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>필요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="나눔명조"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>파우더미니게임</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Roboto"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="나눔명조"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아티팩트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Roboto"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="나눔명조"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>필요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Roboto"/>
+      </rPr>
+      <t>]</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1344,21 +1444,7 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Malgun Gothic"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
       <family val="2"/>
       <charset val="129"/>
     </font>
@@ -1369,6 +1455,26 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Batang"/>
+      <family val="1"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Roboto"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="나눔명조"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="8">
@@ -1466,7 +1572,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1482,7 +1588,6 @@
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
@@ -1495,9 +1600,8 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1727,7 +1831,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="8" customWidth="1"/>
@@ -1793,62 +1897,43 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15">
-      <c r="A3" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="4">
-        <v>1</v>
-      </c>
+    <row r="3" spans="1:8" ht="13">
+      <c r="A3" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="20"/>
+      <c r="C3" s="2"/>
       <c r="H3" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="13">
-      <c r="A4" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="E4" s="4">
-        <v>1</v>
-      </c>
+    <row r="4" spans="1:8" ht="15">
+      <c r="A4" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="2"/>
       <c r="H4" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15">
-      <c r="A5" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="E5" s="4">
-        <v>1</v>
-      </c>
+    <row r="5" spans="1:8" ht="14">
+      <c r="A5" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
       <c r="H5" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="13">
-      <c r="A6" s="7"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-    </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A7" s="7"/>
-      <c r="B7" s="1"/>
-    </row>
-    <row r="11" spans="1:8" ht="13"/>
+    <row r="6" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A6" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B6" s="1"/>
+    </row>
+    <row r="10" spans="1:8" ht="13"/>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1868,67 +1953,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="E1" s="21" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="25" t="s">
+      <c r="D2" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="E2" s="22" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="23"/>
+      <c r="D3" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="E3" s="13" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15">
+      <c r="A4" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="24"/>
-      <c r="D3" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="E3" s="14" t="s">
+      <c r="C4" s="23"/>
+      <c r="D4" s="16" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="15">
-      <c r="A4" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" s="24"/>
-      <c r="D4" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>57</v>
+      <c r="E4" s="13" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1940,825 +2025,799 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="20.33203125" customWidth="1"/>
+    <col min="1" max="1" width="27.33203125" customWidth="1"/>
     <col min="3" max="3" width="26.6640625" customWidth="1"/>
     <col min="4" max="4" width="28" customWidth="1"/>
     <col min="5" max="5" width="42" customWidth="1"/>
     <col min="6" max="6" width="28.83203125" customWidth="1"/>
-    <col min="7" max="7" width="10.83203125" style="20"/>
+    <col min="7" max="7" width="10.83203125" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="16" customFormat="1">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:7" s="15" customFormat="1">
+      <c r="A1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="G1" s="17" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="16" customFormat="1">
-      <c r="A2" s="15" t="s">
+    <row r="2" spans="1:7" s="15" customFormat="1">
+      <c r="A2" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="17" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15">
       <c r="A3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
-      <c r="C3" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" s="19" t="s">
-        <v>24</v>
+      <c r="C3" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15">
       <c r="A4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B4">
         <v>2</v>
       </c>
-      <c r="C4" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E4" s="27" t="s">
+      <c r="C4" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="F4" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" s="19" t="s">
-        <v>26</v>
+      <c r="D4" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="G4" s="18" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B5">
         <v>3</v>
       </c>
-      <c r="C5" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="G5" s="19" t="s">
+      <c r="C5" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" s="18" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15">
       <c r="A6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D6" s="17" t="s">
-        <v>51</v>
+      <c r="E6" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="18" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B7">
-        <v>2</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="E7" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="32">
+      <c r="A8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G7" s="19" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="15">
-      <c r="A8" t="s">
-        <v>49</v>
-      </c>
-      <c r="B8">
-        <v>3</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="E8" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="G8" s="19" t="s">
+      <c r="D8" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="18" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B9">
-        <v>4</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="E9" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="19" t="s">
+      <c r="D9" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" s="18" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15">
       <c r="A10" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B10">
-        <v>5</v>
-      </c>
-      <c r="C10" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="G10" s="18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15">
+      <c r="A11" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11">
+        <v>9</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="G11" s="18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="48">
+      <c r="A12" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12">
+        <v>10</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" s="18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15">
+      <c r="A13" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13">
+        <v>11</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="G13" s="18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15">
+      <c r="A14" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14">
+        <v>12</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G14" s="18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="16">
+      <c r="A15" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15">
+        <v>13</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="E15" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="G15" s="18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="48">
+      <c r="A16" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16">
+        <v>14</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="G16" s="18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="16">
+      <c r="A17" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17">
+        <v>15</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="E17" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="G17" s="18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="16">
+      <c r="A18" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18">
+        <v>16</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="G18" s="18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19">
+        <v>17</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20">
+        <v>18</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="F20" s="13"/>
+    </row>
+    <row r="21" spans="1:7" ht="16">
+      <c r="A21" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21">
+        <v>19</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="G21" s="18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="32">
+      <c r="A22" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22">
+        <v>20</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="E22" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="G22" s="18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="64">
+      <c r="A23" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23">
+        <v>21</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F23" s="13"/>
+      <c r="G23" s="18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="48">
+      <c r="A24" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24">
+        <v>22</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D24" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G24" s="18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="80">
+      <c r="A25" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25">
+        <v>23</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="E25" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="G25" s="18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="128">
+      <c r="A26" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26">
+        <v>24</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="E26" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="F26" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G26" s="18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="80">
+      <c r="A27" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27">
+        <v>25</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D27" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="E27" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G27" s="18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="80">
+      <c r="A28" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B28">
+        <v>26</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="E28" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="G28" s="18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="64">
+      <c r="A29" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29">
+        <v>27</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D29" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F29" s="13"/>
+      <c r="G29" s="18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="48">
+      <c r="A30" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30">
+        <v>28</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D30" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="E30" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="G30" s="18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" s="30" customFormat="1" ht="80">
+      <c r="A31" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="30">
         <v>29</v>
       </c>
-      <c r="E10" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="F10" s="14" t="s">
+      <c r="C31" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="D31" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="E31" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="G31" s="31" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="48">
+      <c r="A32" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32">
+        <v>30</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="E32" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="G32" s="18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="16">
+      <c r="A33" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33">
+        <v>31</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D33" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F33" s="13"/>
+      <c r="G33" s="18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="64">
+      <c r="A34" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34">
+        <v>32</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D34" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="E34" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="G34" s="18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35">
+        <v>33</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F35" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36">
         <v>34</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" ht="32">
-      <c r="A11" t="s">
-        <v>49</v>
-      </c>
-      <c r="B11">
-        <v>6</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D11" s="28" t="s">
-        <v>62</v>
-      </c>
-      <c r="E11" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="G11" s="19" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="15">
-      <c r="A12" t="s">
-        <v>49</v>
-      </c>
-      <c r="B12">
-        <v>7</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="E12" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="G12" s="19" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="15">
-      <c r="A13" t="s">
-        <v>49</v>
-      </c>
-      <c r="B13">
-        <v>8</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="E13" s="14" t="s">
+      <c r="C36" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="F36" s="13"/>
+    </row>
+    <row r="37" spans="1:7" ht="16">
+      <c r="A37" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37">
+        <v>35</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D37" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="E37" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="G13" s="19" t="s">
+      <c r="F37" s="13"/>
+      <c r="G37" s="18" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="15">
-      <c r="A14" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="B14">
-        <v>9</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="G14" s="19" t="s">
+    <row r="38" spans="1:7" ht="32">
+      <c r="A38" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D38" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="E38" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="G38" s="18" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="48">
-      <c r="A15" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B15">
-        <v>10</v>
-      </c>
-      <c r="C15" s="14" t="s">
+    <row r="39" spans="1:7" ht="16">
+      <c r="A39" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="B39">
+        <v>1</v>
+      </c>
+      <c r="C39" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="28" t="s">
-        <v>67</v>
-      </c>
-      <c r="E15" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="G15" s="19" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="15">
-      <c r="A16" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B16">
-        <v>11</v>
-      </c>
-      <c r="C16" s="14" t="s">
+      <c r="D39" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="E39" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="G39" s="18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="16">
+      <c r="A40" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="B40">
+        <v>1</v>
+      </c>
+      <c r="C40" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="E16" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="G16" s="19" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="15">
-      <c r="A17" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B17">
-        <v>12</v>
-      </c>
-      <c r="C17" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="E17" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="F17" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="G17" s="19" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="16">
-      <c r="A18" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B18">
-        <v>13</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="D18" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="E18" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="G18" s="19" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="48">
-      <c r="A19" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B19">
-        <v>14</v>
-      </c>
-      <c r="C19" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="D19" s="28" t="s">
-        <v>71</v>
-      </c>
-      <c r="E19" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="G19" s="19" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="16">
-      <c r="A20" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B20">
-        <v>15</v>
-      </c>
-      <c r="C20" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="D20" s="28" t="s">
-        <v>72</v>
-      </c>
-      <c r="E20" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="G20" s="19" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="16">
-      <c r="A21" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B21">
-        <v>16</v>
-      </c>
-      <c r="C21" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21" s="28" t="s">
-        <v>73</v>
-      </c>
-      <c r="E21" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="G21" s="19" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B22">
-        <v>17</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="F22" s="14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B23">
-        <v>18</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="F23" s="14"/>
-    </row>
-    <row r="24" spans="1:7" ht="16">
-      <c r="A24" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B24">
-        <v>19</v>
-      </c>
-      <c r="C24" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="D24" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="E24" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="G24" s="19" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="32">
-      <c r="A25" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B25">
-        <v>20</v>
-      </c>
-      <c r="C25" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="D25" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="E25" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="G25" s="19" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="64">
-      <c r="A26" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B26">
-        <v>21</v>
-      </c>
-      <c r="C26" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="D26" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E26" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="F26" s="14"/>
-      <c r="G26" s="19" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="48">
-      <c r="A27" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B27">
-        <v>22</v>
-      </c>
-      <c r="C27" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="D27" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="E27" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="F27" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="G27" s="19" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="80">
-      <c r="A28" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B28">
-        <v>23</v>
-      </c>
-      <c r="C28" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="D28" s="28" t="s">
-        <v>79</v>
-      </c>
-      <c r="E28" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="G28" s="19" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="128">
-      <c r="A29" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B29">
-        <v>24</v>
-      </c>
-      <c r="C29" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="D29" s="28" t="s">
-        <v>81</v>
-      </c>
-      <c r="E29" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="F29" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="G29" s="19" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="80">
-      <c r="A30" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B30">
-        <v>25</v>
-      </c>
-      <c r="C30" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="D30" s="28" t="s">
-        <v>82</v>
-      </c>
-      <c r="E30" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="F30" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="G30" s="19" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="80">
-      <c r="A31" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B31">
-        <v>26</v>
-      </c>
-      <c r="C31" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="D31" s="28" t="s">
-        <v>83</v>
-      </c>
-      <c r="E31" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="G31" s="19" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="64">
-      <c r="A32" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B32">
-        <v>27</v>
-      </c>
-      <c r="C32" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="D32" s="28" t="s">
-        <v>84</v>
-      </c>
-      <c r="E32" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="F32" s="14"/>
-      <c r="G32" s="19" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="48">
-      <c r="A33" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B33">
-        <v>28</v>
-      </c>
-      <c r="C33" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="D33" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="E33" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="G33" s="19" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" s="32" customFormat="1" ht="80">
-      <c r="A34" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B34" s="32">
-        <v>29</v>
-      </c>
-      <c r="C34" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="D34" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="E34" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="G34" s="33" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="48">
-      <c r="A35" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B35">
-        <v>30</v>
-      </c>
-      <c r="C35" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="D35" s="28" t="s">
-        <v>87</v>
-      </c>
-      <c r="E35" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="G35" s="19" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="16">
-      <c r="A36" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B36">
-        <v>31</v>
-      </c>
-      <c r="C36" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="D36" s="28" t="s">
+      <c r="D40" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="E40" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="E36" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="F36" s="14"/>
-      <c r="G36" s="19" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="64">
-      <c r="A37" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B37">
-        <v>32</v>
-      </c>
-      <c r="C37" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="D37" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="E37" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="G37" s="19" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B38">
-        <v>33</v>
-      </c>
-      <c r="C38" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="F38" s="14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B39">
-        <v>34</v>
-      </c>
-      <c r="C39" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="F39" s="14"/>
-    </row>
-    <row r="40" spans="1:7" ht="16">
-      <c r="A40" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B40">
-        <v>35</v>
-      </c>
-      <c r="C40" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="D40" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="E40" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="F40" s="14"/>
-      <c r="G40" s="19" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="32">
-      <c r="A41" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="B41">
-        <v>1</v>
-      </c>
-      <c r="C41" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="D41" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="E41" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="G41" s="19" t="s">
+      <c r="G40" s="18" t="s">
         <v>26</v>
       </c>
     </row>

--- a/excel/CutsceneData.xlsx
+++ b/excel/CutsceneData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F71FBA6C-B683-BA42-A831-FE03EFFA282C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AFAF934-9414-B34A-8DFD-67B784FEE57A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4160" yWindow="680" windowWidth="24700" windowHeight="14700" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -862,71 +862,15 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 
-헤헤... 아르바이트로 번 돈을 모조리 쏟아부었거든요…</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>ShowDialog</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 
-덕분에 빈털터리예요..</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 
-그랬군요! 이제 정식으로 마법을 사용할 수 있으니 훌륭한 일자리를 구할 거예요.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>ShowDialog</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 
-마법으로 돌아가는 공장을 차리면 일을 안해도 금을 갈퀴로 쓸어모은다죠? 경력을 쌓아서 마법산업청에 들어가면 명예와 권력을 한 손에 쥘 수도 있고요!</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 
-아아! 마법사의 재능이란 아름다워라!</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 
-그래서 당신은 앞으로 무슨 일을 할 건가요, 마법소녀 새턴?</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 
-아르바이트! 더 많은 아르바이트를 할 거예요!</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">
-...삐삑?!</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 
-아차, 실수로 모국어로 말해버렸네요.
-그래요. 음. 아르바이트.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">
-그럼 서명은 잘 받았고... 여기, 당신 앞으로 온 편지들이에요.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>고마워요!</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 
-그럼, 파트타임 마법소녀! 멋진 인생이 되길!</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -1344,6 +1288,51 @@
       </rPr>
       <t>]</t>
     </r>
+  </si>
+  <si>
+    <t>헤헤... 아르바이트로 번 돈을 모조리 쏟아부었거든요…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>덕분에 빈털터리예요..</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>그랬군요! 이제 정식으로 마법을 사용할 수 있으니 훌륭한 일자리를 구할 거예요.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법으로 돌아가는 공장을 차리면 일을 안해도 금을 갈퀴로 쓸어모은다죠? 경력을 쌓아서 마법산업청에 들어가면 명예와 권력을 한 손에 쥘 수도 있고요!</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>아아! 마법사의 재능이란 아름다워라!</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>그래서 당신은 앞으로 무슨 일을 할 건가요, 마법소녀 새턴?</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>아르바이트! 더 많은 아르바이트를 할 거예요!</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>...삐삑?!</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>아차, 실수로 모국어로 말해버렸네요.
+그래요. 음. 아르바이트.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>그럼 서명은 잘 받았고... 여기, 당신 앞으로 온 편지들이에요.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>그럼, 파트타임 마법소녀! 멋진 인생이 되길!</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1909,7 +1898,7 @@
     </row>
     <row r="4" spans="1:8" ht="15">
       <c r="A4" s="3" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="2"/>
@@ -1919,7 +1908,7 @@
     </row>
     <row r="5" spans="1:8" ht="14">
       <c r="A5" s="7" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -1929,7 +1918,7 @@
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="B6" s="1"/>
     </row>
@@ -2462,7 +2451,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="64">
+    <row r="23" spans="1:7" ht="32">
       <c r="A23" s="13" t="s">
         <v>43</v>
       </c>
@@ -2473,7 +2462,7 @@
         <v>18</v>
       </c>
       <c r="D23" s="26" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="E23" s="13" t="s">
         <v>41</v>
@@ -2483,7 +2472,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="48">
+    <row r="24" spans="1:7" ht="16">
       <c r="A24" s="13" t="s">
         <v>43</v>
       </c>
@@ -2491,10 +2480,10 @@
         <v>22</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D24" s="26" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="E24" s="13" t="s">
         <v>41</v>
@@ -2506,7 +2495,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="80">
+    <row r="25" spans="1:7" ht="48">
       <c r="A25" s="13" t="s">
         <v>43</v>
       </c>
@@ -2517,7 +2506,7 @@
         <v>18</v>
       </c>
       <c r="D25" s="26" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="E25" s="25" t="s">
         <v>42</v>
@@ -2526,7 +2515,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="128">
+    <row r="26" spans="1:7" ht="80">
       <c r="A26" s="13" t="s">
         <v>43</v>
       </c>
@@ -2534,10 +2523,10 @@
         <v>24</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D26" s="26" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="E26" s="25" t="s">
         <v>42</v>
@@ -2549,7 +2538,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="80">
+    <row r="27" spans="1:7" ht="32">
       <c r="A27" s="13" t="s">
         <v>43</v>
       </c>
@@ -2557,10 +2546,10 @@
         <v>25</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D27" s="26" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="E27" s="25" t="s">
         <v>42</v>
@@ -2572,7 +2561,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="80">
+    <row r="28" spans="1:7" ht="32">
       <c r="A28" s="13" t="s">
         <v>43</v>
       </c>
@@ -2583,7 +2572,7 @@
         <v>18</v>
       </c>
       <c r="D28" s="26" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="E28" s="25" t="s">
         <v>42</v>
@@ -2592,7 +2581,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="64">
+    <row r="29" spans="1:7" ht="32">
       <c r="A29" s="13" t="s">
         <v>43</v>
       </c>
@@ -2603,7 +2592,7 @@
         <v>18</v>
       </c>
       <c r="D29" s="26" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="E29" s="13" t="s">
         <v>41</v>
@@ -2613,7 +2602,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="48">
+    <row r="30" spans="1:7" ht="16">
       <c r="A30" s="13" t="s">
         <v>43</v>
       </c>
@@ -2624,7 +2613,7 @@
         <v>18</v>
       </c>
       <c r="D30" s="26" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="E30" s="25" t="s">
         <v>42</v>
@@ -2633,7 +2622,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:7" s="30" customFormat="1" ht="80">
+    <row r="31" spans="1:7" s="30" customFormat="1" ht="48">
       <c r="A31" s="13" t="s">
         <v>43</v>
       </c>
@@ -2644,7 +2633,7 @@
         <v>18</v>
       </c>
       <c r="D31" s="28" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="E31" s="29" t="s">
         <v>42</v>
@@ -2653,7 +2642,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="48">
+    <row r="32" spans="1:7" ht="32">
       <c r="A32" s="13" t="s">
         <v>43</v>
       </c>
@@ -2664,7 +2653,7 @@
         <v>18</v>
       </c>
       <c r="D32" s="26" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="E32" s="25" t="s">
         <v>42</v>
@@ -2684,7 +2673,7 @@
         <v>18</v>
       </c>
       <c r="D33" s="26" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="E33" s="13" t="s">
         <v>41</v>
@@ -2694,7 +2683,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="64">
+    <row r="34" spans="1:7" ht="32">
       <c r="A34" s="13" t="s">
         <v>43</v>
       </c>
@@ -2705,7 +2694,7 @@
         <v>18</v>
       </c>
       <c r="D34" s="26" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="E34" s="25" t="s">
         <v>42</v>
@@ -2751,7 +2740,7 @@
         <v>18</v>
       </c>
       <c r="D37" s="26" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="E37" s="13" t="s">
         <v>41</v>
@@ -2763,7 +2752,7 @@
     </row>
     <row r="38" spans="1:7" ht="32">
       <c r="A38" s="13" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="B38">
         <v>1</v>
@@ -2772,10 +2761,10 @@
         <v>18</v>
       </c>
       <c r="D38" s="26" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G38" s="18" t="s">
         <v>26</v>
@@ -2783,7 +2772,7 @@
     </row>
     <row r="39" spans="1:7" ht="16">
       <c r="A39" s="13" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="B39">
         <v>1</v>
@@ -2792,10 +2781,10 @@
         <v>18</v>
       </c>
       <c r="D39" s="26" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="G39" s="18" t="s">
         <v>26</v>
@@ -2803,7 +2792,7 @@
     </row>
     <row r="40" spans="1:7" ht="16">
       <c r="A40" s="13" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="B40">
         <v>1</v>
@@ -2812,10 +2801,10 @@
         <v>18</v>
       </c>
       <c r="D40" s="26" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G40" s="18" t="s">
         <v>26</v>

--- a/excel/CutsceneData.xlsx
+++ b/excel/CutsceneData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AFAF934-9414-B34A-8DFD-67B784FEE57A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0217687D-F06D-2C47-9474-47D28A33A8CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4160" yWindow="680" windowWidth="24700" windowHeight="14700" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4160" yWindow="680" windowWidth="24700" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CutsceneInfo" sheetId="1" r:id="rId1"/>
@@ -1921,6 +1921,9 @@
         <v>84</v>
       </c>
       <c r="B6" s="1"/>
+      <c r="H6" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:8" ht="13"/>
   </sheetData>

--- a/excel/CutsceneData.xlsx
+++ b/excel/CutsceneData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0217687D-F06D-2C47-9474-47D28A33A8CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05724570-27A6-2743-90FA-4EC70C775C95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4160" yWindow="680" windowWidth="24700" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4160" yWindow="680" windowWidth="24700" windowHeight="14700" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CutsceneInfo" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="99">
   <si>
     <t>list&lt;int&gt;</t>
   </si>
@@ -999,10 +999,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>여긴 지솜님이 다음 빌드에 작업할거야.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>[</t>
     </r>
@@ -1332,6 +1328,62 @@
   </si>
   <si>
     <t>그럼, 파트타임 마법소녀! 멋진 인생이 되길!</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>파우더상점</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>구매</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>뭘 살거임?</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ShowShopPopup</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>PowderShop</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1908,7 +1960,7 @@
     </row>
     <row r="5" spans="1:8" ht="14">
       <c r="A5" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -1918,7 +1970,7 @@
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B6" s="1"/>
       <c r="H6" s="4">
@@ -1934,7 +1986,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -2008,6 +2060,14 @@
         <v>52</v>
       </c>
     </row>
+    <row r="5" spans="1:5" ht="15">
+      <c r="A5" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2017,7 +2077,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="27.33203125" customWidth="1"/>
@@ -2465,7 +2525,7 @@
         <v>18</v>
       </c>
       <c r="D23" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E23" s="13" t="s">
         <v>41</v>
@@ -2486,7 +2546,7 @@
         <v>71</v>
       </c>
       <c r="D24" s="26" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E24" s="13" t="s">
         <v>41</v>
@@ -2509,7 +2569,7 @@
         <v>18</v>
       </c>
       <c r="D25" s="26" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E25" s="25" t="s">
         <v>42</v>
@@ -2529,7 +2589,7 @@
         <v>72</v>
       </c>
       <c r="D26" s="26" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E26" s="25" t="s">
         <v>42</v>
@@ -2552,7 +2612,7 @@
         <v>72</v>
       </c>
       <c r="D27" s="26" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E27" s="25" t="s">
         <v>42</v>
@@ -2575,7 +2635,7 @@
         <v>18</v>
       </c>
       <c r="D28" s="26" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E28" s="25" t="s">
         <v>42</v>
@@ -2595,7 +2655,7 @@
         <v>18</v>
       </c>
       <c r="D29" s="26" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E29" s="13" t="s">
         <v>41</v>
@@ -2616,7 +2676,7 @@
         <v>18</v>
       </c>
       <c r="D30" s="26" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E30" s="25" t="s">
         <v>42</v>
@@ -2636,7 +2696,7 @@
         <v>18</v>
       </c>
       <c r="D31" s="28" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E31" s="29" t="s">
         <v>42</v>
@@ -2656,7 +2716,7 @@
         <v>18</v>
       </c>
       <c r="D32" s="26" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E32" s="25" t="s">
         <v>42</v>
@@ -2697,7 +2757,7 @@
         <v>18</v>
       </c>
       <c r="D34" s="26" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E34" s="25" t="s">
         <v>42</v>
@@ -2753,7 +2813,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="32">
+    <row r="38" spans="1:7" ht="16">
       <c r="A38" s="13" t="s">
         <v>76</v>
       </c>
@@ -2764,7 +2824,7 @@
         <v>18</v>
       </c>
       <c r="D38" s="26" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="E38" s="13" t="s">
         <v>77</v>
@@ -2773,29 +2833,26 @@
         <v>26</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="16">
+    <row r="39" spans="1:7" ht="15">
       <c r="A39" s="13" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D39" s="26" t="s">
-        <v>82</v>
-      </c>
-      <c r="E39" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="G39" s="18" t="s">
-        <v>26</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="D39" s="26"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="G39" s="18"/>
     </row>
     <row r="40" spans="1:7" ht="16">
       <c r="A40" s="13" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B40">
         <v>1</v>
@@ -2804,14 +2861,37 @@
         <v>18</v>
       </c>
       <c r="D40" s="26" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G40" s="18" t="s">
         <v>26</v>
       </c>
+    </row>
+    <row r="41" spans="1:7" ht="16">
+      <c r="A41" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="B41">
+        <v>1</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D41" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="E41" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="G41" s="18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>

--- a/excel/CutsceneData.xlsx
+++ b/excel/CutsceneData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05724570-27A6-2743-90FA-4EC70C775C95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDC3A09A-5866-D842-A912-B7EB6BE90C83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4160" yWindow="680" windowWidth="24700" windowHeight="14700" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4160" yWindow="680" windowWidth="24700" windowHeight="14700" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CutsceneInfo" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="98">
   <si>
     <t>list&lt;int&gt;</t>
   </si>
@@ -1328,50 +1328,6 @@
   </si>
   <si>
     <t>그럼, 파트타임 마법소녀! 멋진 인생이 되길!</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>파우더상점</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>구매</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>]</t>
-    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -2061,12 +2017,8 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="15">
-      <c r="A5" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="B5" s="23" t="s">
-        <v>33</v>
-      </c>
+      <c r="A5" s="13"/>
+      <c r="B5" s="23"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -2824,7 +2776,7 @@
         <v>18</v>
       </c>
       <c r="D38" s="26" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E38" s="13" t="s">
         <v>77</v>
@@ -2841,12 +2793,12 @@
         <v>2</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D39" s="26"/>
       <c r="E39" s="13"/>
       <c r="F39" s="13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G39" s="18"/>
     </row>

--- a/excel/CutsceneData.xlsx
+++ b/excel/CutsceneData.xlsx
@@ -8,21 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDC3A09A-5866-D842-A912-B7EB6BE90C83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B314E7F4-8552-2049-9FE6-484BDB0CBC62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4160" yWindow="680" windowWidth="24700" windowHeight="14700" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CutsceneInfo" sheetId="1" r:id="rId1"/>
-    <sheet name="CutsceneSelection" sheetId="3" r:id="rId2"/>
-    <sheet name="Cutscene" sheetId="2" r:id="rId3"/>
+    <sheet name="Cutscene" sheetId="2" r:id="rId2"/>
+    <sheet name="CutsceneSelection" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="103">
   <si>
     <t>list&lt;int&gt;</t>
   </si>
@@ -1340,6 +1340,130 @@
   </si>
   <si>
     <t>PowderShop</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>솜사탕상점</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>구매</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>솜사탕상점</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>구매</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]</t>
+    </r>
+  </si>
+  <si>
+    <t>CottonCandyShop</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>미카</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>뭘 살거임??</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1933,6 +2057,14 @@
         <v>1</v>
       </c>
     </row>
+    <row r="7" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A7" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="H7" s="4">
+        <v>1</v>
+      </c>
+    </row>
     <row r="10" spans="1:8" ht="13"/>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -1941,6 +2073,861 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:G43"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="13"/>
+  <cols>
+    <col min="1" max="1" width="27.33203125" customWidth="1"/>
+    <col min="3" max="3" width="26.6640625" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="5" max="5" width="42" customWidth="1"/>
+    <col min="6" max="6" width="28.83203125" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" style="19"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="15" customFormat="1">
+      <c r="A1" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" s="15" customFormat="1">
+      <c r="A2" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15">
+      <c r="A3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15">
+      <c r="A4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="G4" s="18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15">
+      <c r="A5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" s="18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15">
+      <c r="A6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15">
+      <c r="A7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="32">
+      <c r="A8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15">
+      <c r="A9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" s="18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15">
+      <c r="A10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10">
+        <v>8</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="G10" s="18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15">
+      <c r="A11" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11">
+        <v>9</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="G11" s="18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="48">
+      <c r="A12" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12">
+        <v>10</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" s="18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15">
+      <c r="A13" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13">
+        <v>11</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="G13" s="18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15">
+      <c r="A14" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14">
+        <v>12</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G14" s="18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="16">
+      <c r="A15" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15">
+        <v>13</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="E15" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="G15" s="18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="48">
+      <c r="A16" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16">
+        <v>14</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="G16" s="18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="16">
+      <c r="A17" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17">
+        <v>15</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="E17" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="G17" s="18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="16">
+      <c r="A18" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18">
+        <v>16</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="G18" s="18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19">
+        <v>17</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20">
+        <v>18</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="F20" s="13"/>
+    </row>
+    <row r="21" spans="1:7" ht="16">
+      <c r="A21" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21">
+        <v>19</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="G21" s="18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="32">
+      <c r="A22" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22">
+        <v>20</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="E22" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="G22" s="18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="32">
+      <c r="A23" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23">
+        <v>21</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F23" s="13"/>
+      <c r="G23" s="18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="16">
+      <c r="A24" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24">
+        <v>22</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="D24" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G24" s="18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="48">
+      <c r="A25" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25">
+        <v>23</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="E25" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="G25" s="18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="80">
+      <c r="A26" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26">
+        <v>24</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D26" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="E26" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="F26" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G26" s="18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="32">
+      <c r="A27" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27">
+        <v>25</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D27" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="E27" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G27" s="18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="32">
+      <c r="A28" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B28">
+        <v>26</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="E28" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="G28" s="18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="32">
+      <c r="A29" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29">
+        <v>27</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D29" s="26" t="s">
+        <v>90</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F29" s="13"/>
+      <c r="G29" s="18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="16">
+      <c r="A30" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30">
+        <v>28</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D30" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="E30" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="G30" s="18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" s="30" customFormat="1" ht="48">
+      <c r="A31" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="30">
+        <v>29</v>
+      </c>
+      <c r="C31" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="D31" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="E31" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="G31" s="31" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="32">
+      <c r="A32" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32">
+        <v>30</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="E32" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="G32" s="18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="16">
+      <c r="A33" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33">
+        <v>31</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D33" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F33" s="13"/>
+      <c r="G33" s="18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="32">
+      <c r="A34" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34">
+        <v>32</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D34" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="E34" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="G34" s="18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35">
+        <v>33</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F35" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36">
+        <v>34</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="F36" s="13"/>
+    </row>
+    <row r="37" spans="1:7" ht="16">
+      <c r="A37" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37">
+        <v>35</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D37" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="E37" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F37" s="13"/>
+      <c r="G37" s="18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="16">
+      <c r="A38" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D38" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="E38" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="G38" s="18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="15">
+      <c r="A39" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B39">
+        <v>2</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="D39" s="26"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="G39" s="18"/>
+    </row>
+    <row r="40" spans="1:7" ht="16">
+      <c r="A40" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="B40">
+        <v>1</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D40" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="E40" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="G40" s="18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="16">
+      <c r="A41" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="B41">
+        <v>1</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D41" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="E41" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="G41" s="18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="16">
+      <c r="A42" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="B42">
+        <v>1</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D42" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="E42" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="G42" s="18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="15">
+      <c r="A43" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="B43">
+        <v>2</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="F43" s="13" t="s">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="13"/>
@@ -2025,828 +3012,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="13"/>
-  <cols>
-    <col min="1" max="1" width="27.33203125" customWidth="1"/>
-    <col min="3" max="3" width="26.6640625" customWidth="1"/>
-    <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="5" width="42" customWidth="1"/>
-    <col min="6" max="6" width="28.83203125" customWidth="1"/>
-    <col min="7" max="7" width="10.83203125" style="19"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" s="15" customFormat="1">
-      <c r="A1" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E1" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="G1" s="17" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" s="15" customFormat="1">
-      <c r="A2" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="15">
-      <c r="A3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D3" s="16" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15">
-      <c r="A4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="G4" s="18" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="15">
-      <c r="A5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="E5" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="G5" s="18" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="15">
-      <c r="A6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="18" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="15">
-      <c r="A7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="32">
-      <c r="A8" t="s">
-        <v>44</v>
-      </c>
-      <c r="B8">
-        <v>6</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="E8" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="G8" s="18" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15">
-      <c r="A9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B9">
-        <v>7</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="E9" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="G9" s="18" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="15">
-      <c r="A10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10">
-        <v>8</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="G10" s="18" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="15">
-      <c r="A11" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="B11">
-        <v>9</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="G11" s="18" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="48">
-      <c r="A12" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B12">
-        <v>10</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="E12" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="G12" s="18" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="15">
-      <c r="A13" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B13">
-        <v>11</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="G13" s="18" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="15">
-      <c r="A14" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14">
-        <v>12</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="G14" s="18" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="16">
-      <c r="A15" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15">
-        <v>13</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D15" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="E15" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="G15" s="18" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="48">
-      <c r="A16" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16">
-        <v>14</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="G16" s="18" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="16">
-      <c r="A17" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B17">
-        <v>15</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="E17" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="G17" s="18" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="16">
-      <c r="A18" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B18">
-        <v>16</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D18" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="G18" s="18" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B19">
-        <v>17</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B20">
-        <v>18</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="F20" s="13"/>
-    </row>
-    <row r="21" spans="1:7" ht="16">
-      <c r="A21" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B21">
-        <v>19</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21" s="26" t="s">
-        <v>69</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="G21" s="18" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="32">
-      <c r="A22" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B22">
-        <v>20</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D22" s="26" t="s">
-        <v>70</v>
-      </c>
-      <c r="E22" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="G22" s="18" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="32">
-      <c r="A23" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B23">
-        <v>21</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D23" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="F23" s="13"/>
-      <c r="G23" s="18" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="16">
-      <c r="A24" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B24">
-        <v>22</v>
-      </c>
-      <c r="C24" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="D24" s="26" t="s">
-        <v>85</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="F24" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="G24" s="18" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="48">
-      <c r="A25" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B25">
-        <v>23</v>
-      </c>
-      <c r="C25" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D25" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="E25" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="G25" s="18" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="80">
-      <c r="A26" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B26">
-        <v>24</v>
-      </c>
-      <c r="C26" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="D26" s="26" t="s">
-        <v>87</v>
-      </c>
-      <c r="E26" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="F26" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="G26" s="18" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="32">
-      <c r="A27" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B27">
-        <v>25</v>
-      </c>
-      <c r="C27" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="D27" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="E27" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="G27" s="18" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="32">
-      <c r="A28" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B28">
-        <v>26</v>
-      </c>
-      <c r="C28" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D28" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="E28" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="G28" s="18" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="32">
-      <c r="A29" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B29">
-        <v>27</v>
-      </c>
-      <c r="C29" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D29" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="F29" s="13"/>
-      <c r="G29" s="18" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="16">
-      <c r="A30" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B30">
-        <v>28</v>
-      </c>
-      <c r="C30" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D30" s="26" t="s">
-        <v>91</v>
-      </c>
-      <c r="E30" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="G30" s="18" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" s="30" customFormat="1" ht="48">
-      <c r="A31" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31" s="30">
-        <v>29</v>
-      </c>
-      <c r="C31" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="D31" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="E31" s="29" t="s">
-        <v>42</v>
-      </c>
-      <c r="G31" s="31" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="32">
-      <c r="A32" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B32">
-        <v>30</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D32" s="26" t="s">
-        <v>93</v>
-      </c>
-      <c r="E32" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="G32" s="18" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="16">
-      <c r="A33" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B33">
-        <v>31</v>
-      </c>
-      <c r="C33" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D33" s="26" t="s">
-        <v>73</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="F33" s="13"/>
-      <c r="G33" s="18" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="32">
-      <c r="A34" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B34">
-        <v>32</v>
-      </c>
-      <c r="C34" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D34" s="26" t="s">
-        <v>94</v>
-      </c>
-      <c r="E34" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="G34" s="18" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B35">
-        <v>33</v>
-      </c>
-      <c r="C35" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F35" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B36">
-        <v>34</v>
-      </c>
-      <c r="C36" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="F36" s="13"/>
-    </row>
-    <row r="37" spans="1:7" ht="16">
-      <c r="A37" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B37">
-        <v>35</v>
-      </c>
-      <c r="C37" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D37" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="E37" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="F37" s="13"/>
-      <c r="G37" s="18" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="16">
-      <c r="A38" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="B38">
-        <v>1</v>
-      </c>
-      <c r="C38" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D38" s="26" t="s">
-        <v>95</v>
-      </c>
-      <c r="E38" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="G38" s="18" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="15">
-      <c r="A39" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="B39">
-        <v>2</v>
-      </c>
-      <c r="C39" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="D39" s="26"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="G39" s="18"/>
-    </row>
-    <row r="40" spans="1:7" ht="16">
-      <c r="A40" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="B40">
-        <v>1</v>
-      </c>
-      <c r="C40" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D40" s="26" t="s">
-        <v>81</v>
-      </c>
-      <c r="E40" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="G40" s="18" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="16">
-      <c r="A41" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="B41">
-        <v>1</v>
-      </c>
-      <c r="C41" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D41" s="26" t="s">
-        <v>81</v>
-      </c>
-      <c r="E41" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="G41" s="18" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42" s="13"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/excel/CutsceneData.xlsx
+++ b/excel/CutsceneData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B314E7F4-8552-2049-9FE6-484BDB0CBC62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{777484FF-0595-6B4D-95CE-EE149169EAC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4160" yWindow="680" windowWidth="24700" windowHeight="14700" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4160" yWindow="680" windowWidth="24700" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CutsceneInfo" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="106">
   <si>
     <t>list&lt;int&gt;</t>
   </si>
@@ -1436,6 +1436,10 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
+    <t>뭘 살거임??</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <t>[</t>
     </r>
@@ -1443,10 +1447,75 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>솜사탕미니게임</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아티팩트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>필요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
       </rPr>
       <t>미카</t>
     </r>
@@ -1463,7 +1532,89 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>뭘 살거임??</t>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>리피파이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>솜사탕미니게임</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Roboto"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아티팩트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Roboto"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>필요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Roboto"/>
+      </rPr>
+      <t>]</t>
+    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1693,7 +1844,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1734,6 +1885,7 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1952,7 +2104,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="8" customWidth="1"/>
@@ -2058,14 +2210,23 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A7" s="13" t="s">
-        <v>98</v>
-      </c>
+      <c r="A7" s="32" t="s">
+        <v>105</v>
+      </c>
+      <c r="B7" s="1"/>
       <c r="H7" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="13"/>
+    <row r="8" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A8" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="H8" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="13"/>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2074,7 +2235,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="27.33203125" customWidth="1"/>
@@ -2881,7 +3042,7 @@
         <v>81</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="G41" s="18" t="s">
         <v>26</v>
@@ -2889,7 +3050,7 @@
     </row>
     <row r="42" spans="1:7" ht="16">
       <c r="A42" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B42">
         <v>1</v>
@@ -2898,26 +3059,46 @@
         <v>18</v>
       </c>
       <c r="D42" s="26" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G42" s="18" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="15">
+    <row r="43" spans="1:7" ht="16">
       <c r="A43" s="13" t="s">
         <v>99</v>
       </c>
       <c r="B43">
+        <v>1</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D43" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="E43" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="G43" s="18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="15">
+      <c r="A44" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="B44">
         <v>2</v>
       </c>
-      <c r="C43" s="13" t="s">
+      <c r="C44" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="F43" s="13" t="s">
+      <c r="F44" s="13" t="s">
         <v>100</v>
       </c>
     </row>
